--- a/pic_sheets.xlsx
+++ b/pic_sheets.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="Voltage Divider" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,8 @@
     <sheet name="INA238" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="INA SAMPLE" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Proportion" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="lists" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Iexp" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="lists" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="ADC_BITS" vbProcedure="false">lists!$B$2:$B$3</definedName>
@@ -36,6 +37,9 @@
     <definedName function="false" hidden="false" name="DAC_VSOURCEP" vbProcedure="false">PIC16F1503_DAC!$C$3</definedName>
     <definedName function="false" hidden="false" name="DCxB" vbProcedure="false">PWM!$B$13</definedName>
     <definedName function="false" hidden="false" name="HIGH_LIMIT" vbProcedure="false">'Pot step'!$B$4</definedName>
+    <definedName function="false" hidden="false" name="IEXP_AMPLITUDE" vbProcedure="false">Iexp!$D$2</definedName>
+    <definedName function="false" hidden="false" name="IEXP_KEXP" vbProcedure="false">Iexp!$D$3</definedName>
+    <definedName function="false" hidden="false" name="IEXP_KEXP_DIV" vbProcedure="false">Iexp!$D$4</definedName>
     <definedName function="false" hidden="false" name="INA238_BOVL" vbProcedure="false">INA238!$C$28</definedName>
     <definedName function="false" hidden="false" name="INA238_BUVL" vbProcedure="false">INA238!$C$29</definedName>
     <definedName function="false" hidden="false" name="INA238_CURRENT_LSB" vbProcedure="false">INA238!$C$22</definedName>
@@ -186,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="234">
   <si>
     <t xml:space="preserve">VOLTAGE DIVISOR</t>
   </si>
@@ -2978,6 +2982,21 @@
     <t xml:space="preserve">Use this formula in your code and rename constants as it is needed.</t>
   </si>
   <si>
+    <t xml:space="preserve">Amplitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kexp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kexp divisor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iexp</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADC 8 bits</t>
   </si>
   <si>
@@ -2988,29 +3007,28 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="20">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="General"/>
-    <numFmt numFmtId="171" formatCode="0.00000"/>
-    <numFmt numFmtId="172" formatCode="0.000%"/>
-    <numFmt numFmtId="173" formatCode="0"/>
-    <numFmt numFmtId="174" formatCode="0.0000000%"/>
-    <numFmt numFmtId="175" formatCode="0.000000000"/>
-    <numFmt numFmtId="176" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="178" formatCode="0.0"/>
-    <numFmt numFmtId="179" formatCode="0.000000"/>
-    <numFmt numFmtId="180" formatCode="##0.0000E+0"/>
-    <numFmt numFmtId="181" formatCode="0.0000000000"/>
-    <numFmt numFmtId="182" formatCode="0.000000000000"/>
-    <numFmt numFmtId="183" formatCode="0.0000000"/>
+    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="173" formatCode="0.0000000%"/>
+    <numFmt numFmtId="174" formatCode="0.000000000"/>
+    <numFmt numFmtId="175" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0.000000"/>
+    <numFmt numFmtId="179" formatCode="##0.0000E+0"/>
+    <numFmt numFmtId="180" formatCode="0.0000000000"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000"/>
+    <numFmt numFmtId="182" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3101,7 +3119,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -3258,6 +3276,11 @@
       <name val="Courier New"/>
       <family val="3"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3543,7 +3566,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3688,7 +3711,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3696,15 +3719,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3712,15 +3735,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="3" borderId="6" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="5" fillId="3" borderId="6" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3732,11 +3755,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="3" borderId="6" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="6" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -3868,7 +3891,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -3876,7 +3899,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3932,7 +3955,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3956,7 +3979,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="15" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3968,7 +3991,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4036,11 +4059,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -4052,7 +4075,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4068,11 +4091,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="9" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="9" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4100,7 +4123,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4108,7 +4131,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4144,7 +4167,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="179" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4164,7 +4187,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4212,19 +4235,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="180" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="180" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="181" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4232,7 +4255,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4260,7 +4283,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4274,6 +4297,10 @@
     </xf>
     <xf numFmtId="164" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4350,10 +4377,10 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFFF420E"/>
       <rgbColor rgb="FF4A7EBB"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF004586"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
@@ -4378,18 +4405,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1200" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1200" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1200" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Voutrb</a:t>
@@ -4444,10 +4470,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
@@ -4461,6 +4488,15 @@
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -4473,307 +4509,307 @@
               <c:strCache>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>0.00</c:v>
+                  <c:v>0,00</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47.00</c:v>
+                  <c:v>47,00</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.00</c:v>
+                  <c:v>94,00</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>141.00</c:v>
+                  <c:v>141,00</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>188.00</c:v>
+                  <c:v>188,00</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>235.00</c:v>
+                  <c:v>235,00</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>282.00</c:v>
+                  <c:v>282,00</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>329.00</c:v>
+                  <c:v>329,00</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>376.00</c:v>
+                  <c:v>376,00</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>423.00</c:v>
+                  <c:v>423,00</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>470.00</c:v>
+                  <c:v>470,00</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>517.00</c:v>
+                  <c:v>517,00</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>564.00</c:v>
+                  <c:v>564,00</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>611.00</c:v>
+                  <c:v>611,00</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>658.00</c:v>
+                  <c:v>658,00</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>705.00</c:v>
+                  <c:v>705,00</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>752.00</c:v>
+                  <c:v>752,00</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>799.00</c:v>
+                  <c:v>799,00</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>846.00</c:v>
+                  <c:v>846,00</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>893.00</c:v>
+                  <c:v>893,00</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>940.00</c:v>
+                  <c:v>940,00</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>987.00</c:v>
+                  <c:v>987,00</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1034.00</c:v>
+                  <c:v>1034,00</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1081.00</c:v>
+                  <c:v>1081,00</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1128.00</c:v>
+                  <c:v>1128,00</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1175.00</c:v>
+                  <c:v>1175,00</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1222.00</c:v>
+                  <c:v>1222,00</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1269.00</c:v>
+                  <c:v>1269,00</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1316.00</c:v>
+                  <c:v>1316,00</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1363.00</c:v>
+                  <c:v>1363,00</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1410.00</c:v>
+                  <c:v>1410,00</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1457.00</c:v>
+                  <c:v>1457,00</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1504.00</c:v>
+                  <c:v>1504,00</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1551.00</c:v>
+                  <c:v>1551,00</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1598.00</c:v>
+                  <c:v>1598,00</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1645.00</c:v>
+                  <c:v>1645,00</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1692.00</c:v>
+                  <c:v>1692,00</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1739.00</c:v>
+                  <c:v>1739,00</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1786.00</c:v>
+                  <c:v>1786,00</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1833.00</c:v>
+                  <c:v>1833,00</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1880.00</c:v>
+                  <c:v>1880,00</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1927.00</c:v>
+                  <c:v>1927,00</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1974.00</c:v>
+                  <c:v>1974,00</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2021.00</c:v>
+                  <c:v>2021,00</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2068.00</c:v>
+                  <c:v>2068,00</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2115.00</c:v>
+                  <c:v>2115,00</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2162.00</c:v>
+                  <c:v>2162,00</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2209.00</c:v>
+                  <c:v>2209,00</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2256.00</c:v>
+                  <c:v>2256,00</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2303.00</c:v>
+                  <c:v>2303,00</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2350.00</c:v>
+                  <c:v>2350,00</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2397.00</c:v>
+                  <c:v>2397,00</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2444.00</c:v>
+                  <c:v>2444,00</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2491.00</c:v>
+                  <c:v>2491,00</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2538.00</c:v>
+                  <c:v>2538,00</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2585.00</c:v>
+                  <c:v>2585,00</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2632.00</c:v>
+                  <c:v>2632,00</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2679.00</c:v>
+                  <c:v>2679,00</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2726.00</c:v>
+                  <c:v>2726,00</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2773.00</c:v>
+                  <c:v>2773,00</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2820.00</c:v>
+                  <c:v>2820,00</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2867.00</c:v>
+                  <c:v>2867,00</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2914.00</c:v>
+                  <c:v>2914,00</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2961.00</c:v>
+                  <c:v>2961,00</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>3008.00</c:v>
+                  <c:v>3008,00</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>3055.00</c:v>
+                  <c:v>3055,00</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>3102.00</c:v>
+                  <c:v>3102,00</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>3149.00</c:v>
+                  <c:v>3149,00</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>3196.00</c:v>
+                  <c:v>3196,00</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>3243.00</c:v>
+                  <c:v>3243,00</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>3290.00</c:v>
+                  <c:v>3290,00</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>3337.00</c:v>
+                  <c:v>3337,00</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>3384.00</c:v>
+                  <c:v>3384,00</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>3431.00</c:v>
+                  <c:v>3431,00</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>3478.00</c:v>
+                  <c:v>3478,00</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>3525.00</c:v>
+                  <c:v>3525,00</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>3572.00</c:v>
+                  <c:v>3572,00</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>3619.00</c:v>
+                  <c:v>3619,00</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>3666.00</c:v>
+                  <c:v>3666,00</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>3713.00</c:v>
+                  <c:v>3713,00</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>3760.00</c:v>
+                  <c:v>3760,00</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>3807.00</c:v>
+                  <c:v>3807,00</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>3854.00</c:v>
+                  <c:v>3854,00</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>3901.00</c:v>
+                  <c:v>3901,00</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>3948.00</c:v>
+                  <c:v>3948,00</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>3995.00</c:v>
+                  <c:v>3995,00</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>4042.00</c:v>
+                  <c:v>4042,00</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>4089.00</c:v>
+                  <c:v>4089,00</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>4136.00</c:v>
+                  <c:v>4136,00</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>4183.00</c:v>
+                  <c:v>4183,00</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>4230.00</c:v>
+                  <c:v>4230,00</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>4277.00</c:v>
+                  <c:v>4277,00</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>4324.00</c:v>
+                  <c:v>4324,00</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>4371.00</c:v>
+                  <c:v>4371,00</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>4418.00</c:v>
+                  <c:v>4418,00</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>4465.00</c:v>
+                  <c:v>4465,00</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>4512.00</c:v>
+                  <c:v>4512,00</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>4559.00</c:v>
+                  <c:v>4559,00</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>4606.00</c:v>
+                  <c:v>4606,00</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>4653.00</c:v>
+                  <c:v>4653,00</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>4700.00</c:v>
+                  <c:v>4700,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5100,11 +5136,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69198498"/>
-        <c:axId val="18379854"/>
+        <c:axId val="14480622"/>
+        <c:axId val="97737264"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69198498"/>
+        <c:axId val="14480622"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5127,16 +5163,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18379854"/>
+        <c:crossAx val="97737264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5144,7 +5181,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18379854"/>
+        <c:axId val="97737264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5177,16 +5214,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69198498"/>
+        <c:crossAx val="14480622"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5211,10 +5249,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -5250,18 +5289,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1200" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1200" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1200" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Voutra</a:t>
@@ -5316,10 +5354,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
@@ -5333,6 +5372,15 @@
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -5345,307 +5393,307 @@
               <c:strCache>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>0.00</c:v>
+                  <c:v>0,00</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47.00</c:v>
+                  <c:v>47,00</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.00</c:v>
+                  <c:v>94,00</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>141.00</c:v>
+                  <c:v>141,00</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>188.00</c:v>
+                  <c:v>188,00</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>235.00</c:v>
+                  <c:v>235,00</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>282.00</c:v>
+                  <c:v>282,00</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>329.00</c:v>
+                  <c:v>329,00</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>376.00</c:v>
+                  <c:v>376,00</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>423.00</c:v>
+                  <c:v>423,00</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>470.00</c:v>
+                  <c:v>470,00</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>517.00</c:v>
+                  <c:v>517,00</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>564.00</c:v>
+                  <c:v>564,00</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>611.00</c:v>
+                  <c:v>611,00</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>658.00</c:v>
+                  <c:v>658,00</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>705.00</c:v>
+                  <c:v>705,00</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>752.00</c:v>
+                  <c:v>752,00</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>799.00</c:v>
+                  <c:v>799,00</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>846.00</c:v>
+                  <c:v>846,00</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>893.00</c:v>
+                  <c:v>893,00</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>940.00</c:v>
+                  <c:v>940,00</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>987.00</c:v>
+                  <c:v>987,00</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1034.00</c:v>
+                  <c:v>1034,00</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1081.00</c:v>
+                  <c:v>1081,00</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1128.00</c:v>
+                  <c:v>1128,00</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1175.00</c:v>
+                  <c:v>1175,00</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1222.00</c:v>
+                  <c:v>1222,00</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1269.00</c:v>
+                  <c:v>1269,00</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1316.00</c:v>
+                  <c:v>1316,00</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1363.00</c:v>
+                  <c:v>1363,00</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1410.00</c:v>
+                  <c:v>1410,00</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1457.00</c:v>
+                  <c:v>1457,00</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1504.00</c:v>
+                  <c:v>1504,00</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1551.00</c:v>
+                  <c:v>1551,00</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1598.00</c:v>
+                  <c:v>1598,00</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1645.00</c:v>
+                  <c:v>1645,00</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1692.00</c:v>
+                  <c:v>1692,00</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1739.00</c:v>
+                  <c:v>1739,00</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1786.00</c:v>
+                  <c:v>1786,00</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1833.00</c:v>
+                  <c:v>1833,00</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1880.00</c:v>
+                  <c:v>1880,00</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1927.00</c:v>
+                  <c:v>1927,00</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1974.00</c:v>
+                  <c:v>1974,00</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2021.00</c:v>
+                  <c:v>2021,00</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2068.00</c:v>
+                  <c:v>2068,00</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2115.00</c:v>
+                  <c:v>2115,00</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2162.00</c:v>
+                  <c:v>2162,00</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2209.00</c:v>
+                  <c:v>2209,00</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2256.00</c:v>
+                  <c:v>2256,00</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2303.00</c:v>
+                  <c:v>2303,00</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2350.00</c:v>
+                  <c:v>2350,00</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2397.00</c:v>
+                  <c:v>2397,00</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2444.00</c:v>
+                  <c:v>2444,00</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2491.00</c:v>
+                  <c:v>2491,00</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2538.00</c:v>
+                  <c:v>2538,00</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2585.00</c:v>
+                  <c:v>2585,00</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2632.00</c:v>
+                  <c:v>2632,00</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2679.00</c:v>
+                  <c:v>2679,00</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2726.00</c:v>
+                  <c:v>2726,00</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2773.00</c:v>
+                  <c:v>2773,00</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2820.00</c:v>
+                  <c:v>2820,00</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2867.00</c:v>
+                  <c:v>2867,00</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2914.00</c:v>
+                  <c:v>2914,00</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2961.00</c:v>
+                  <c:v>2961,00</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>3008.00</c:v>
+                  <c:v>3008,00</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>3055.00</c:v>
+                  <c:v>3055,00</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>3102.00</c:v>
+                  <c:v>3102,00</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>3149.00</c:v>
+                  <c:v>3149,00</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>3196.00</c:v>
+                  <c:v>3196,00</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>3243.00</c:v>
+                  <c:v>3243,00</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>3290.00</c:v>
+                  <c:v>3290,00</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>3337.00</c:v>
+                  <c:v>3337,00</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>3384.00</c:v>
+                  <c:v>3384,00</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>3431.00</c:v>
+                  <c:v>3431,00</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>3478.00</c:v>
+                  <c:v>3478,00</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>3525.00</c:v>
+                  <c:v>3525,00</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>3572.00</c:v>
+                  <c:v>3572,00</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>3619.00</c:v>
+                  <c:v>3619,00</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>3666.00</c:v>
+                  <c:v>3666,00</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>3713.00</c:v>
+                  <c:v>3713,00</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>3760.00</c:v>
+                  <c:v>3760,00</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>3807.00</c:v>
+                  <c:v>3807,00</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>3854.00</c:v>
+                  <c:v>3854,00</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>3901.00</c:v>
+                  <c:v>3901,00</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>3948.00</c:v>
+                  <c:v>3948,00</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>3995.00</c:v>
+                  <c:v>3995,00</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>4042.00</c:v>
+                  <c:v>4042,00</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>4089.00</c:v>
+                  <c:v>4089,00</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>4136.00</c:v>
+                  <c:v>4136,00</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>4183.00</c:v>
+                  <c:v>4183,00</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>4230.00</c:v>
+                  <c:v>4230,00</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>4277.00</c:v>
+                  <c:v>4277,00</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>4324.00</c:v>
+                  <c:v>4324,00</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>4371.00</c:v>
+                  <c:v>4371,00</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>4418.00</c:v>
+                  <c:v>4418,00</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>4465.00</c:v>
+                  <c:v>4465,00</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>4512.00</c:v>
+                  <c:v>4512,00</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>4559.00</c:v>
+                  <c:v>4559,00</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>4606.00</c:v>
+                  <c:v>4606,00</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>4653.00</c:v>
+                  <c:v>4653,00</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>4700.00</c:v>
+                  <c:v>4700,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5972,11 +6020,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="38830157"/>
-        <c:axId val="91244505"/>
+        <c:axId val="80820268"/>
+        <c:axId val="14035230"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38830157"/>
+        <c:axId val="80820268"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5999,16 +6047,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91244505"/>
+        <c:crossAx val="14035230"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6016,7 +6065,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91244505"/>
+        <c:axId val="14035230"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6049,16 +6098,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38830157"/>
+        <c:crossAx val="80820268"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6083,10 +6133,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
@@ -6154,10 +6205,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
@@ -6171,6 +6223,15 @@
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -9837,10 +9898,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
@@ -9854,6 +9916,15 @@
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -13486,11 +13557,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="80141560"/>
-        <c:axId val="45658018"/>
+        <c:axId val="71217552"/>
+        <c:axId val="69272438"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="80141560"/>
+        <c:axId val="71217552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13523,21 +13594,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45658018"/>
+        <c:crossAx val="69272438"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="45658018"/>
+        <c:axId val="69272438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13580,16 +13652,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80141560"/>
+        <c:crossAx val="71217552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -13617,6 +13690,912 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Iexp!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ir</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Iexp!$C$6:$C$105</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>0.429718054085704</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.472512583845</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.47842170341898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.15243476732624</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.91479835337545</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.7978087328771</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.56661835452229</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.25145002008501</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.92770459670308</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3396047101184</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.76278640269062</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.76734911622094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.143657504437381</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.76417901795027</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.39647250332093</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.91161555645122</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.03163643115471</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9.13627948174564</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.34785135312001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.34761470705458</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.02852176924358</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.11346037363947</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.9091919687514</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.57123950854067</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.75308626048612</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.34246233628112</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.37658827383372</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.66488349361064</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.46585156150162</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.18685074929166</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.95738944279886</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.478054254008229</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.0617341070777</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.905034790089204</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5.54388045036535</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.13614801896476</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.36919714178484</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8.54045530577482</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.03969305994991</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6.70431480719509</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.203723957435818</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.45951803729013</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.88699783716559</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5.77602140881495</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.13075763405629</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.987615636557546</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6.53169717333032</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.79550029947342</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8.26429179647023</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7.91691014153609</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8.62360945298526</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.8389161715945</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.81765768453945</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.26974710899971</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.63907368670983</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6.61991475687462</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>8.0829857813601</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4.71229770209408</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3.50487998238251</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.34483472650516</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.88373745083259</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6.80104749707036</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3.50562102548064</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>8.29914385994893</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4.17504907163683</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.73301750273906</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9.15644826953628</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9.43106018364307</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1.1165548858185</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.69873877400054</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.60469422991423</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.511300075760364</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7.25298552633013</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8.56108632561108</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6.60707456556352</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.32376315876179</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9.51356761293524</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>8.44197970476428</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7.35334765787976</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>8.31226112036589</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2.60362861102948</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5.8194740892925</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>3.99632682966279</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.55023463574087</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>8.5317631127461</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>3.93922935991368</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.4181353093813</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.510459817814127</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.05316488865555</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>7.18481972310827</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>8.66907387260781</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2.61628547137463</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5.391254675496</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5.96581244322181</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2.70657448545943</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>7.97034157198372</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.0469588778146307</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>2.48493751718923</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>3.98431785323413</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2.29942331716446</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Iexp!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Iexp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Iexp!$D$6:$D$105</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>0.429718054085704</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.03827696003756</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.52630590871385</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.65153168043633</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.10418501502415</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.24290975859474</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.70765147778025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.2164111862412</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.95866986833358</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.63485683669054</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.66044274989056</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.28182402315663</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.25419071941278</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.95618837912028</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.24424520396041</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.17771927445857</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.7485027057978</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.22605806098737</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.6504167194139</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.78985631694203</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.03758940740234</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.05276360064977</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.22404927427009</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.29348732112421</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.98540710899659</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.4568181544535</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.24077217832954</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.12559444138576</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.59364586540893</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.31228684218548</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.44130736230815</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.24865674064817</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.81127221393408</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.0300247291651</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.33279587340515</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.09346630251707</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.74861247037063</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5.50698103745146</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5.01352344195115</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5.35168171499994</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4.32209016348712</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5.14957573824772</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5.09706015803129</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5.23285240818802</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.81243345336168</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.04746989000085</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.54431534666674</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.19455233722808</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.00850022907651</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.59018221156843</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>6.19686765985179</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.32527736220033</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.42375342666816</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.39295216313447</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4.84217646784954</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.19772412565456</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.77477645679567</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.56228070585535</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.15080056116078</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.98960739422966</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4.36843340555024</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4.85495622385427</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4.58508918417954</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.32790011933342</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.0973299097941</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.42446742838309</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.37086359661373</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.1829029140196</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.16963330837938</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.27545440150361</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.34130236718573</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.37530190890066</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.95083863238655</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.67288817103146</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.85972544993787</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.75253299170266</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>6.50473991594917</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6.89218787371219</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>6.98441983054571</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>7.24998808850974</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6.32071619301369</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6.22046777226945</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.77563958374812</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.73055859414667</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6.29079949786656</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.82048547027598</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.54001543809704</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.53410431404046</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.63791642896348</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.14729708779244</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.85165244475551</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5.20457905007934</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5.24191417516267</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5.3866938287745</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4.85066996011148</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.47460428248593</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4.38907520155167</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4.00824766467918</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.00346170239017</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>3.66265402534503</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="80465716"/>
+        <c:axId val="52490007"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="80465716"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="52490007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="52490007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="80465716"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -13628,18 +14607,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>138960</xdr:colOff>
+      <xdr:colOff>138600</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>36360</xdr:rowOff>
+      <xdr:rowOff>52920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 2"/>
+        <xdr:cNvPr id="1" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11946240" y="1057320"/>
-        <a:ext cx="4783320" cy="3520440"/>
+        <a:ext cx="4782960" cy="3520080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -13654,22 +14633,22 @@
       <xdr:col>26</xdr:col>
       <xdr:colOff>247680</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>28440</xdr:rowOff>
+      <xdr:rowOff>45360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>138960</xdr:colOff>
+      <xdr:colOff>138600</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>97200</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 3"/>
+        <xdr:cNvPr id="2" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11946240" y="4569840"/>
-        <a:ext cx="4783320" cy="3434400"/>
+        <a:ext cx="4782960" cy="3434040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -13688,18 +14667,18 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>38160</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>47520</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>138960</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>91080</xdr:rowOff>
+      <xdr:colOff>138600</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>109800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr=" V(t) = V_0(1-e^{-t/ \tau}) "/>
+        <xdr:cNvPr id="3" name="Picture 1" descr=" V(t) = V_0(1-e^{-t/ \tau}) "/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13709,11 +14688,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3863520" y="2981160"/>
-          <a:ext cx="1679400" cy="234000"/>
+          <a:ext cx="1679040" cy="233640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13730,18 +14710,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>607320</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>119880</xdr:rowOff>
+      <xdr:colOff>606960</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>138600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="4" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5704920" y="190440"/>
-        <a:ext cx="5480280" cy="3815640"/>
+        <a:ext cx="5479920" cy="3815280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -13765,13 +14745,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>510120</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:colOff>509760</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>62280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1" descr=""/>
+        <xdr:cNvPr id="5" name="Picture 1" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13781,11 +14761,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4928760" y="0"/>
-          <a:ext cx="2325600" cy="2539080"/>
+          <a:ext cx="2325240" cy="2538720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13802,13 +14783,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>329040</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:colOff>328680</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 2" descr=""/>
+        <xdr:cNvPr id="6" name="Picture 2" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13818,11 +14799,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7355880" y="76320"/>
-          <a:ext cx="2774880" cy="2139120"/>
+          <a:ext cx="2774520" cy="2138760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13834,18 +14816,18 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>76320</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>66600</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>510120</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>24120</xdr:rowOff>
+      <xdr:colOff>509760</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>147600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 3" descr=""/>
+        <xdr:cNvPr id="7" name="Picture 3" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13855,11 +14837,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4835160" y="2695680"/>
-          <a:ext cx="2419200" cy="2433960"/>
+          <a:ext cx="2418840" cy="2433600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13871,18 +14854,18 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>95400</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>319680</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:colOff>319320</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>167040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 5" descr=""/>
+        <xdr:cNvPr id="8" name="Picture 5" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13892,11 +14875,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7451280" y="2857680"/>
-          <a:ext cx="2670120" cy="1424520"/>
+          <a:ext cx="2669760" cy="1424160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13908,18 +14892,18 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38160</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>95400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>109800</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:colOff>109440</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>81360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 6" descr=""/>
+        <xdr:cNvPr id="9" name="Picture 6" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13929,11 +14913,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5838840"/>
-          <a:ext cx="3035160" cy="2272320"/>
+          <a:ext cx="3034800" cy="2271960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13945,18 +14930,18 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>152280</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38160</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>95400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>52560</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>158040</xdr:rowOff>
+      <xdr:colOff>52200</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>24480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 7" descr=""/>
+        <xdr:cNvPr id="10" name="Picture 7" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -13966,11 +14951,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3077640" y="5838840"/>
-          <a:ext cx="3107880" cy="882000"/>
+          <a:ext cx="3107520" cy="881640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -13982,18 +14968,18 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>200160</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>95400</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>138600</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>119880</xdr:rowOff>
+      <xdr:colOff>138240</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>176400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 8" descr=""/>
+        <xdr:cNvPr id="11" name="Picture 8" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -14003,11 +14989,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3125520" y="6848640"/>
-          <a:ext cx="3146040" cy="405360"/>
+          <a:ext cx="3145680" cy="405000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -14019,18 +15006,18 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>528840</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>52920</xdr:rowOff>
+      <xdr:colOff>528480</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>109440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 9" descr=""/>
+        <xdr:cNvPr id="12" name="Picture 9" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -14040,16 +15027,52 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6132960" y="5810040"/>
-          <a:ext cx="3586320" cy="1567440"/>
+          <a:ext cx="3585960" cy="1567080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>97560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>746640</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>136440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5548680" y="973800"/>
+        <a:ext cx="9383400" cy="5121360"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -14236,7 +15259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:AA1048576"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="1.04"/>
@@ -14304,7 +15327,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="13" t="str">
         <f aca="false">CONCATENATE(TEXT(VD_VIN-VD_VOUT,"0.###"),"V")</f>
-        <v>2.789V</v>
+        <v>2,789V</v>
       </c>
       <c r="H4" s="14"/>
       <c r="T4" s="12"/>
@@ -14330,7 +15353,7 @@
       <c r="I6" s="19"/>
       <c r="T6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="7" t="s">
         <v>5</v>
       </c>
@@ -14342,14 +15365,14 @@
       </c>
       <c r="H7" s="20"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="9"/>
       <c r="G8" s="13" t="str">
         <f aca="false">CONCATENATE(TEXT(VD_VOUT,"0.###"),"V")</f>
-        <v>0.211V</v>
+        <v>0,211V</v>
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="22" t="s">
@@ -14376,7 +15399,7 @@
       <c r="Y8" s="25"/>
       <c r="Z8" s="25"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="3"/>
@@ -15139,7 +16162,7 @@
         <v>0.0292760058136749</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="35" t="s">
         <v>37</v>
       </c>
@@ -17017,23 +18040,18 @@
     <mergeCell ref="Q22:S23"/>
     <mergeCell ref="I24:S24"/>
   </mergeCells>
-  <conditionalFormatting sqref="J19">
+  <conditionalFormatting sqref="J19 N19 R19">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>1023</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N19 R19">
+  <conditionalFormatting sqref="J20 N20 R20">
     <cfRule type="cellIs" priority="3" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>1023</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J20 N20 R20">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>255</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J21 N21 R21">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>4095</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17059,8 +18077,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="2.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.07"/>
@@ -17086,7 +18104,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="148" t="s">
         <v>117</v>
       </c>
@@ -17097,7 +18115,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="148" t="s">
         <v>119</v>
       </c>
@@ -17108,7 +18126,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="148" t="s">
         <v>120</v>
       </c>
@@ -17128,7 +18146,7 @@
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="148" t="s">
         <v>122</v>
       </c>
@@ -17159,7 +18177,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="148" t="s">
         <v>126</v>
       </c>
@@ -17190,7 +18208,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="148" t="s">
         <v>129</v>
       </c>
@@ -17221,7 +18239,7 @@
       <c r="F9" s="155"/>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="148" t="s">
         <v>131</v>
       </c>
@@ -17242,7 +18260,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="148" t="s">
         <v>133</v>
       </c>
@@ -17274,7 +18292,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28"/>
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
@@ -17299,7 +18317,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="148" t="s">
         <v>138</v>
       </c>
@@ -17320,7 +18338,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="148" t="s">
         <v>140</v>
       </c>
@@ -17331,7 +18349,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="148" t="s">
         <v>140</v>
       </c>
@@ -17363,8 +18381,7 @@
       <c r="J18" s="159"/>
       <c r="K18" s="159"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="148" t="s">
         <v>143</v>
       </c>
@@ -17385,7 +18402,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="148" t="s">
         <v>145</v>
       </c>
@@ -17406,7 +18423,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="148" t="s">
         <v>147</v>
       </c>
@@ -17428,7 +18445,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="148" t="s">
         <v>149</v>
       </c>
@@ -17472,7 +18489,6 @@
       <c r="J26" s="159"/>
       <c r="K26" s="159"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E5:K5"/>
@@ -17499,7 +18515,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.69"/>
@@ -17652,7 +18668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="163" t="s">
         <v>174</v>
       </c>
@@ -17665,7 +18681,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="163" t="s">
         <v>176</v>
       </c>
@@ -17877,7 +18893,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:I23"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.73"/>
@@ -18202,7 +19218,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.43"/>
@@ -18240,6 +19256,7 @@
       <c r="D4" s="174"/>
       <c r="E4" s="174"/>
     </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="175" t="s">
         <v>218</v>
@@ -18339,8 +19356,1665 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A2:D105"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.8"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="183" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="183" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.79111070315503</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.429718054085704</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <f aca="false">C6</f>
+        <v>0.429718054085704</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.54599599329903</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>8.472512583845</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <f aca="false">D6+(IEXP_KEXP/IEXP_KEXP_DIV)*(C7-D6)</f>
+        <v>2.03827696003756</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.12011797404225</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>4.47842170341898</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <f aca="false">D7+(IEXP_KEXP/IEXP_KEXP_DIV)*(C8-D7)</f>
+        <v>2.52630590871385</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.76042327143065</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>8.15243476732624</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <f aca="false">D8+(IEXP_KEXP/IEXP_KEXP_DIV)*(C9-D8)</f>
+        <v>3.65153168043633</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.43308914726334</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>5.91479835337545</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <f aca="false">D9+(IEXP_KEXP/IEXP_KEXP_DIV)*(C10-D9)</f>
+        <v>4.10418501502415</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.84284194260299</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>9.7978087328771</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <f aca="false">D10+(IEXP_KEXP/IEXP_KEXP_DIV)*(C11-D10)</f>
+        <v>5.24290975859474</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.19567046665071</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>7.56661835452229</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <f aca="false">D11+(IEXP_KEXP/IEXP_KEXP_DIV)*(C12-D11)</f>
+        <v>5.70765147778025</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.59448899956465</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>3.25145002008501</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <f aca="false">D12+(IEXP_KEXP/IEXP_KEXP_DIV)*(C13-D12)</f>
+        <v>5.2164111862412</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.86928455810361</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>3.92770459670308</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <f aca="false">D13+(IEXP_KEXP/IEXP_KEXP_DIV)*(C14-D13)</f>
+        <v>4.95866986833358</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.07826396152705</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>3.3396047101184</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <f aca="false">D14+(IEXP_KEXP/IEXP_KEXP_DIV)*(C15-D14)</f>
+        <v>4.63485683669054</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.11705275955308</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>9.76278640269062</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <f aca="false">D15+(IEXP_KEXP/IEXP_KEXP_DIV)*(C16-D15)</f>
+        <v>5.66044274989056</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.33476300839875</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>3.76734911622094</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <f aca="false">D16+(IEXP_KEXP/IEXP_KEXP_DIV)*(C17-D16)</f>
+        <v>5.28182402315663</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.79851321062579</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>0.143657504437381</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <f aca="false">D17+(IEXP_KEXP/IEXP_KEXP_DIV)*(C18-D17)</f>
+        <v>4.25419071941278</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.15539051503872</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>7.76417901795027</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <f aca="false">D18+(IEXP_KEXP/IEXP_KEXP_DIV)*(C19-D18)</f>
+        <v>4.95618837912028</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.16487089811229</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>6.39647250332093</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <f aca="false">D19+(IEXP_KEXP/IEXP_KEXP_DIV)*(C20-D19)</f>
+        <v>5.24424520396041</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.00736283648328</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>9.91161555645122</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <f aca="false">D20+(IEXP_KEXP/IEXP_KEXP_DIV)*(C21-D20)</f>
+        <v>6.17771927445857</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.58015286610421</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>9.03163643115471</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <f aca="false">D21+(IEXP_KEXP/IEXP_KEXP_DIV)*(C22-D21)</f>
+        <v>6.7485027057978</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.72519133420921</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>9.13627948174564</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <f aca="false">D22+(IEXP_KEXP/IEXP_KEXP_DIV)*(C23-D22)</f>
+        <v>7.22605806098737</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.39002658963395</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>4.34785135312001</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <f aca="false">D23+(IEXP_KEXP/IEXP_KEXP_DIV)*(C24-D23)</f>
+        <v>6.6504167194139</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.3588912294557</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>7.34761470705458</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <f aca="false">D24+(IEXP_KEXP/IEXP_KEXP_DIV)*(C25-D24)</f>
+        <v>6.78985631694203</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.61058243443729</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>3.02852176924358</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <f aca="false">D25+(IEXP_KEXP/IEXP_KEXP_DIV)*(C26-D25)</f>
+        <v>6.03758940740234</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.87617002351889</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>6.11346037363947</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <f aca="false">D26+(IEXP_KEXP/IEXP_KEXP_DIV)*(C27-D26)</f>
+        <v>6.05276360064977</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.69998400292463</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>6.9091919687514</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <f aca="false">D27+(IEXP_KEXP/IEXP_KEXP_DIV)*(C28-D27)</f>
+        <v>6.22404927427009</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.05606528759426</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>6.57123950854067</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <f aca="false">D28+(IEXP_KEXP/IEXP_KEXP_DIV)*(C29-D28)</f>
+        <v>6.29348732112421</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.20830181424804</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>4.75308626048612</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <f aca="false">D29+(IEXP_KEXP/IEXP_KEXP_DIV)*(C30-D29)</f>
+        <v>5.98540710899659</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.62054451729341</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>3.34246233628112</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <f aca="false">D30+(IEXP_KEXP/IEXP_KEXP_DIV)*(C31-D30)</f>
+        <v>5.4568181544535</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.75426433867156</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>4.37658827383372</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <f aca="false">D31+(IEXP_KEXP/IEXP_KEXP_DIV)*(C32-D31)</f>
+        <v>5.24077217832954</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.87722427664708</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>9.66488349361064</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <f aca="false">D32+(IEXP_KEXP/IEXP_KEXP_DIV)*(C33-D32)</f>
+        <v>6.12559444138576</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.648557052335569</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>8.46585156150162</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <f aca="false">D33+(IEXP_KEXP/IEXP_KEXP_DIV)*(C34-D33)</f>
+        <v>6.59364586540893</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.82266233571511</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>5.18685074929166</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <f aca="false">D34+(IEXP_KEXP/IEXP_KEXP_DIV)*(C35-D34)</f>
+        <v>6.31228684218548</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.97287546984628</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>6.95738944279886</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <f aca="false">D35+(IEXP_KEXP/IEXP_KEXP_DIV)*(C36-D35)</f>
+        <v>6.44130736230815</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.0882868839632196</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>0.478054254008229</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <f aca="false">D36+(IEXP_KEXP/IEXP_KEXP_DIV)*(C37-D36)</f>
+        <v>5.24865674064817</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.59401547855547</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>3.0617341070777</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <f aca="false">D37+(IEXP_KEXP/IEXP_KEXP_DIV)*(C38-D37)</f>
+        <v>4.81127221393408</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.30715700726693</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>0.905034790089204</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <f aca="false">D38+(IEXP_KEXP/IEXP_KEXP_DIV)*(C39-D38)</f>
+        <v>4.0300247291651</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.51630141477397</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>5.54388045036535</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <f aca="false">D39+(IEXP_KEXP/IEXP_KEXP_DIV)*(C40-D39)</f>
+        <v>4.33279587340515</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.55260605128734</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>3.13614801896476</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <f aca="false">D40+(IEXP_KEXP/IEXP_KEXP_DIV)*(C41-D40)</f>
+        <v>4.09346630251707</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.10985068731873</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>7.36919714178484</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <f aca="false">D41+(IEXP_KEXP/IEXP_KEXP_DIV)*(C42-D41)</f>
+        <v>4.74861247037063</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.99936504267065</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>8.54045530577482</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <f aca="false">D42+(IEXP_KEXP/IEXP_KEXP_DIV)*(C43-D42)</f>
+        <v>5.50698103745146</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.58071534686771</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>3.03969305994991</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <f aca="false">D43+(IEXP_KEXP/IEXP_KEXP_DIV)*(C44-D43)</f>
+        <v>5.01352344195115</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.24146121017282</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>6.70431480719509</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <f aca="false">D44+(IEXP_KEXP/IEXP_KEXP_DIV)*(C45-D44)</f>
+        <v>5.35168171499994</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.79860879665514</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>0.203723957435818</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <f aca="false">D45+(IEXP_KEXP/IEXP_KEXP_DIV)*(C46-D45)</f>
+        <v>4.32209016348712</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.268103706588215</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>8.45951803729013</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <f aca="false">D46+(IEXP_KEXP/IEXP_KEXP_DIV)*(C47-D46)</f>
+        <v>5.14957573824772</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.49230414474772</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>4.88699783716559</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <f aca="false">D47+(IEXP_KEXP/IEXP_KEXP_DIV)*(C48-D47)</f>
+        <v>5.09706015803129</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.664500623597921</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>5.77602140881495</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <f aca="false">D48+(IEXP_KEXP/IEXP_KEXP_DIV)*(C49-D48)</f>
+        <v>5.23285240818802</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.76438456668519</v>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>3.13075763405629</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <f aca="false">D49+(IEXP_KEXP/IEXP_KEXP_DIV)*(C50-D49)</f>
+        <v>4.81243345336168</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.51289718937891</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>0.987615636557546</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <f aca="false">D50+(IEXP_KEXP/IEXP_KEXP_DIV)*(C51-D50)</f>
+        <v>4.04746989000085</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.22486166033124</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>6.53169717333032</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <f aca="false">D51+(IEXP_KEXP/IEXP_KEXP_DIV)*(C52-D51)</f>
+        <v>4.54431534666674</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.27018217974863</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>2.79550029947342</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <f aca="false">D52+(IEXP_KEXP/IEXP_KEXP_DIV)*(C53-D52)</f>
+        <v>4.19455233722808</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.23088099726691</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>8.26429179647023</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <f aca="false">D53+(IEXP_KEXP/IEXP_KEXP_DIV)*(C54-D53)</f>
+        <v>5.00850022907651</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.94954383217157</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>7.91691014153609</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <f aca="false">D54+(IEXP_KEXP/IEXP_KEXP_DIV)*(C55-D54)</f>
+        <v>5.59018221156843</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.34789379806231</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>8.62360945298526</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <f aca="false">D55+(IEXP_KEXP/IEXP_KEXP_DIV)*(C56-D55)</f>
+        <v>6.19686765985179</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.97906111048827</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>1.8389161715945</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <f aca="false">D56+(IEXP_KEXP/IEXP_KEXP_DIV)*(C57-D56)</f>
+        <v>5.32527736220033</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.03132368527573</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>5.81765768453945</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <f aca="false">D57+(IEXP_KEXP/IEXP_KEXP_DIV)*(C58-D57)</f>
+        <v>5.42375342666816</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.69628231412157</v>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>5.26974710899971</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <f aca="false">D58+(IEXP_KEXP/IEXP_KEXP_DIV)*(C59-D58)</f>
+        <v>5.39295216313447</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.21696963258405</v>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>2.63907368670983</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <f aca="false">D59+(IEXP_KEXP/IEXP_KEXP_DIV)*(C60-D59)</f>
+        <v>4.84217646784954</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.85430685210585</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>6.61991475687462</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <f aca="false">D60+(IEXP_KEXP/IEXP_KEXP_DIV)*(C61-D60)</f>
+        <v>5.19772412565456</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.9987763890124</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>8.0829857813601</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <f aca="false">D61+(IEXP_KEXP/IEXP_KEXP_DIV)*(C62-D61)</f>
+        <v>5.77477645679567</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.61531157647147</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>4.71229770209408</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <f aca="false">D62+(IEXP_KEXP/IEXP_KEXP_DIV)*(C63-D62)</f>
+        <v>5.56228070585535</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.0972400781918017</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>3.50487998238251</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <f aca="false">D63+(IEXP_KEXP/IEXP_KEXP_DIV)*(C64-D63)</f>
+        <v>5.15080056116078</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.08095077121734</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>4.34483472650516</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <f aca="false">D64+(IEXP_KEXP/IEXP_KEXP_DIV)*(C65-D64)</f>
+        <v>4.98960739422966</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.63378190387373</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>1.88373745083259</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <f aca="false">D65+(IEXP_KEXP/IEXP_KEXP_DIV)*(C66-D65)</f>
+        <v>4.36843340555024</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.140809046935067</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>6.80104749707036</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <f aca="false">D66+(IEXP_KEXP/IEXP_KEXP_DIV)*(C67-D66)</f>
+        <v>4.85495622385427</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.47349510726976</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>3.50562102548064</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <f aca="false">D67+(IEXP_KEXP/IEXP_KEXP_DIV)*(C68-D67)</f>
+        <v>4.58508918417954</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>9.62736453843547</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>8.29914385994893</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <f aca="false">D68+(IEXP_KEXP/IEXP_KEXP_DIV)*(C69-D68)</f>
+        <v>5.32790011933342</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.6620120943322</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>4.17504907163683</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <f aca="false">D69+(IEXP_KEXP/IEXP_KEXP_DIV)*(C70-D69)</f>
+        <v>5.0973299097941</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.33686092431355</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>1.73301750273906</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <f aca="false">D70+(IEXP_KEXP/IEXP_KEXP_DIV)*(C71-D70)</f>
+        <v>4.42446742838309</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.73802265013446</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>9.15644826953628</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <f aca="false">D71+(IEXP_KEXP/IEXP_KEXP_DIV)*(C72-D71)</f>
+        <v>5.37086359661373</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.47861559326571</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>9.43106018364307</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <f aca="false">D72+(IEXP_KEXP/IEXP_KEXP_DIV)*(C73-D72)</f>
+        <v>6.1829029140196</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.41651900308579</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>1.1165548858185</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <f aca="false">D73+(IEXP_KEXP/IEXP_KEXP_DIV)*(C74-D73)</f>
+        <v>5.16963330837938</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.30346223753705</v>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>5.69873877400054</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <f aca="false">D74+(IEXP_KEXP/IEXP_KEXP_DIV)*(C75-D74)</f>
+        <v>5.27545440150361</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>5.7079312575367</v>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>5.60469422991423</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <f aca="false">D75+(IEXP_KEXP/IEXP_KEXP_DIV)*(C76-D75)</f>
+        <v>5.34130236718573</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.04405577094155</v>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>0.511300075760364</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <f aca="false">D76+(IEXP_KEXP/IEXP_KEXP_DIV)*(C77-D76)</f>
+        <v>4.37530190890066</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.89263465633161</v>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>7.25298552633013</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <f aca="false">D77+(IEXP_KEXP/IEXP_KEXP_DIV)*(C78-D77)</f>
+        <v>4.95083863238655</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.39537422244525</v>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>8.56108632561108</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <f aca="false">D78+(IEXP_KEXP/IEXP_KEXP_DIV)*(C79-D78)</f>
+        <v>5.67288817103146</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.98182188175249</v>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>6.60707456556352</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <f aca="false">D79+(IEXP_KEXP/IEXP_KEXP_DIV)*(C80-D79)</f>
+        <v>5.85972544993787</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.81032418091853</v>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>5.32376315876179</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <f aca="false">D80+(IEXP_KEXP/IEXP_KEXP_DIV)*(C81-D80)</f>
+        <v>5.75253299170266</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.91058547311034</v>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>9.51356761293524</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <f aca="false">D81+(IEXP_KEXP/IEXP_KEXP_DIV)*(C82-D81)</f>
+        <v>6.50473991594917</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.10597831720326</v>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>8.44197970476428</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <f aca="false">D82+(IEXP_KEXP/IEXP_KEXP_DIV)*(C83-D82)</f>
+        <v>6.89218787371219</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.58830592913759</v>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>7.35334765787976</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <f aca="false">D83+(IEXP_KEXP/IEXP_KEXP_DIV)*(C84-D83)</f>
+        <v>6.98441983054571</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.962663452132504</v>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>8.31226112036589</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <f aca="false">D84+(IEXP_KEXP/IEXP_KEXP_DIV)*(C85-D84)</f>
+        <v>7.24998808850974</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.79403858712773</v>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>2.60362861102948</v>
+      </c>
+      <c r="D86" s="0" t="n">
+        <f aca="false">D85+(IEXP_KEXP/IEXP_KEXP_DIV)*(C86-D85)</f>
+        <v>6.32071619301369</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.07079343006117</v>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>5.8194740892925</v>
+      </c>
+      <c r="D87" s="0" t="n">
+        <f aca="false">D86+(IEXP_KEXP/IEXP_KEXP_DIV)*(C87-D86)</f>
+        <v>6.22046777226945</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.05346991981214</v>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>3.99632682966279</v>
+      </c>
+      <c r="D88" s="0" t="n">
+        <f aca="false">D87+(IEXP_KEXP/IEXP_KEXP_DIV)*(C88-D87)</f>
+        <v>5.77563958374812</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.81663781852328</v>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>5.55023463574087</v>
+      </c>
+      <c r="D89" s="0" t="n">
+        <f aca="false">D88+(IEXP_KEXP/IEXP_KEXP_DIV)*(C89-D88)</f>
+        <v>5.73055859414667</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>4.66120051658273</v>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>8.5317631127461</v>
+      </c>
+      <c r="D90" s="0" t="n">
+        <f aca="false">D89+(IEXP_KEXP/IEXP_KEXP_DIV)*(C90-D89)</f>
+        <v>6.29079949786656</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.0129421484657</v>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>3.93922935991368</v>
+      </c>
+      <c r="D91" s="0" t="n">
+        <f aca="false">D90+(IEXP_KEXP/IEXP_KEXP_DIV)*(C91-D90)</f>
+        <v>5.82048547027598</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.29996786904711</v>
+      </c>
+      <c r="B92" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>4.4181353093813</v>
+      </c>
+      <c r="D92" s="0" t="n">
+        <f aca="false">D91+(IEXP_KEXP/IEXP_KEXP_DIV)*(C92-D91)</f>
+        <v>5.54001543809704</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.426173687455738</v>
+      </c>
+      <c r="B93" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>0.510459817814127</v>
+      </c>
+      <c r="D93" s="0" t="n">
+        <f aca="false">D92+(IEXP_KEXP/IEXP_KEXP_DIV)*(C93-D92)</f>
+        <v>4.53410431404046</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>6.71115622841354</v>
+      </c>
+      <c r="B94" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>5.05316488865555</v>
+      </c>
+      <c r="D94" s="0" t="n">
+        <f aca="false">D93+(IEXP_KEXP/IEXP_KEXP_DIV)*(C94-D93)</f>
+        <v>4.63791642896348</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>8.18103260016991</v>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>7.18481972310827</v>
+      </c>
+      <c r="D95" s="0" t="n">
+        <f aca="false">D94+(IEXP_KEXP/IEXP_KEXP_DIV)*(C95-D94)</f>
+        <v>5.14729708779244</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.17409182813817</v>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>8.66907387260781</v>
+      </c>
+      <c r="D96" s="0" t="n">
+        <f aca="false">D95+(IEXP_KEXP/IEXP_KEXP_DIV)*(C96-D95)</f>
+        <v>5.85165244475551</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.80028785856429</v>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>2.61628547137463</v>
+      </c>
+      <c r="D97" s="0" t="n">
+        <f aca="false">D96+(IEXP_KEXP/IEXP_KEXP_DIV)*(C97-D96)</f>
+        <v>5.20457905007934</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.29737914390737</v>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>5.391254675496</v>
+      </c>
+      <c r="D98" s="0" t="n">
+        <f aca="false">D97+(IEXP_KEXP/IEXP_KEXP_DIV)*(C98-D97)</f>
+        <v>5.24191417516267</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.10312404973368</v>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>5.96581244322181</v>
+      </c>
+      <c r="D99" s="0" t="n">
+        <f aca="false">D98+(IEXP_KEXP/IEXP_KEXP_DIV)*(C99-D98)</f>
+        <v>5.3866938287745</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>3.25584447282897</v>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>2.70657448545943</v>
+      </c>
+      <c r="D100" s="0" t="n">
+        <f aca="false">D99+(IEXP_KEXP/IEXP_KEXP_DIV)*(C100-D99)</f>
+        <v>4.85066996011148</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.679658435699403</v>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>7.97034157198372</v>
+      </c>
+      <c r="D101" s="0" t="n">
+        <f aca="false">D100+(IEXP_KEXP/IEXP_KEXP_DIV)*(C101-D100)</f>
+        <v>5.47460428248593</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>2.95565862635884</v>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>0.0469588778146307</v>
+      </c>
+      <c r="D102" s="0" t="n">
+        <f aca="false">D101+(IEXP_KEXP/IEXP_KEXP_DIV)*(C102-D101)</f>
+        <v>4.38907520155167</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>0.26818544382084</v>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>2.48493751718923</v>
+      </c>
+      <c r="D103" s="0" t="n">
+        <f aca="false">D102+(IEXP_KEXP/IEXP_KEXP_DIV)*(C103-D102)</f>
+        <v>4.00824766467918</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>1.97809793202947</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="C104" s="0" t="n">
+        <v>3.98431785323413</v>
+      </c>
+      <c r="D104" s="0" t="n">
+        <f aca="false">D103+(IEXP_KEXP/IEXP_KEXP_DIV)*(C104-D103)</f>
+        <v>4.00346170239017</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="n">
+        <f aca="true">IEXP_AMPLITUDE*RAND()</f>
+        <v>7.26061716944749</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>2.29942331716446</v>
+      </c>
+      <c r="D105" s="0" t="n">
+        <f aca="false">D104+(IEXP_KEXP/IEXP_KEXP_DIV)*(C105-D104)</f>
+        <v>3.66265402534503</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A2:B3"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.7"/>
   </cols>
@@ -18350,12 +21024,12 @@
         <v>35</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="142" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B3" s="142" t="s">
         <v>57</v>
@@ -18378,7 +21052,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="C2:O39"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="1.04"/>
@@ -18785,7 +21459,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:V23"/>
-  <sheetFormatPr defaultColWidth="8.3203125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.3203125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="85" width="3.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="85" width="1.04"/>
@@ -19100,7 +21774,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:O622"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="1.04"/>
@@ -19198,8 +21872,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="53"/>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I14" s="22" t="s">
         <v>3</v>
       </c>
@@ -19220,7 +21893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I15" s="121" t="s">
         <v>1</v>
       </c>
@@ -19241,7 +21914,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I16" s="22"/>
       <c r="J16" s="73"/>
       <c r="K16" s="34"/>
@@ -19256,7 +21929,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="22" t="s">
         <v>63</v>
       </c>
@@ -19267,7 +21940,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="126" t="s">
         <v>69</v>
       </c>
@@ -28330,7 +31003,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F5"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.69"/>
@@ -28343,7 +31016,7 @@
       <c r="D2" s="128"/>
       <c r="E2" s="128"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="35" t="s">
         <v>72</v>
       </c>
@@ -28415,7 +31088,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.09"/>
@@ -28433,8 +31106,7 @@
       <c r="D1" s="130"/>
       <c r="E1" s="130"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="35" t="s">
         <v>79</v>
       </c>
@@ -28465,7 +31137,7 @@
         <v>15625</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
         <v>83</v>
       </c>
@@ -28481,7 +31153,7 @@
         <v>3.1875</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
         <v>85</v>
       </c>
@@ -28502,7 +31174,7 @@
         <v>37987</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
         <v>88</v>
       </c>
@@ -28534,7 +31206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35"/>
       <c r="B8" s="131" t="n">
         <v>1</v>
@@ -28544,7 +31216,7 @@
       <c r="K8" s="28"/>
       <c r="L8" s="28"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="35"/>
       <c r="B9" s="131" t="n">
         <v>4</v>
@@ -28554,7 +31226,7 @@
       <c r="K9" s="28"/>
       <c r="L9" s="28"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35"/>
       <c r="B10" s="131" t="n">
         <v>16</v>
@@ -28564,7 +31236,7 @@
       <c r="K10" s="28"/>
       <c r="L10" s="28"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="35"/>
       <c r="B11" s="131" t="n">
         <v>64</v>
@@ -28574,7 +31246,7 @@
       <c r="K11" s="28"/>
       <c r="L11" s="28"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="35" t="s">
         <v>90</v>
       </c>
@@ -28606,7 +31278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="35" t="s">
         <v>92</v>
       </c>
@@ -28718,7 +31390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="133" t="n">
         <v>0.11</v>
       </c>
@@ -28737,7 +31409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="136" t="s">
         <v>95</v>
       </c>
@@ -28914,7 +31586,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.36"/>
@@ -29034,7 +31706,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="2.34"/>
   </cols>
@@ -29044,7 +31716,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="142" t="s">
         <v>106</v>
       </c>
@@ -29055,7 +31727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="142" t="s">
         <v>107</v>
       </c>
@@ -29083,7 +31755,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="2.2"/>
   </cols>
@@ -29093,8 +31765,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
         <v>109</v>
       </c>
@@ -29105,7 +31776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
         <v>110</v>
       </c>
@@ -29116,7 +31787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
         <v>111</v>
       </c>
